--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:32:33+00:00</t>
+    <t>2026-03-17T11:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:52:23+00:00</t>
+    <t>2026-03-18T09:27:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:27:49+00:00</t>
+    <t>2026-03-18T09:50:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:50:43+00:00</t>
+    <t>2026-03-18T09:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:00+00:00</t>
+    <t>2026-03-18T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:59:20+00:00</t>
+    <t>2026-03-18T10:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T10:14:32+00:00</t>
+    <t>2026-03-18T10:58:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-NEWS2score.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.1</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T10:58:54+00:00</t>
+    <t>2026-03-18T11:31:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
